--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487582_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487582_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1513</v>
+        <v>2.466</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9856</v>
+        <v>2.2203</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8342</v>
+        <v>0.2457</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5544</v>
+        <v>-1.2528</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3164</v>
+        <v>-0.2084</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.238</v>
+        <v>-1.0444</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3511</v>
+        <v>1.2032</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0875</v>
+        <v>1.8249</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2635</v>
+        <v>-0.6217</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9054</v>
+        <v>-2.456</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4039</v>
+        <v>-2.0333</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5015</v>
+        <v>-0.4227</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5224</v>
+        <v>2.7164</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5224</v>
+        <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0937</v>
+        <v>0.5128</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6345</v>
+        <v>0.4051</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4592</v>
+        <v>0.1077</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.9104</v>
+        <v>0.4895</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9104</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1765</v>
+        <v>1.5458</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1354</v>
+        <v>3.6955</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.959</v>
+        <v>-2.1497</v>
       </c>
       <c r="G3" t="n">
         <v>3.1814</v>
@@ -688,13 +688,13 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0011</v>
+        <v>0.3704</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0576</v>
+        <v>0.6177</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0565</v>
+        <v>-0.2473</v>
       </c>
       <c r="V3" t="n">
         <v>0.5164</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7781</v>
+        <v>1.3198</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6677</v>
+        <v>2.1277</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8078</v>
       </c>
       <c r="G4" t="n">
         <v>-2.0665</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0863</v>
+        <v>0.6281</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4322</v>
+        <v>0.8922</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3459</v>
+        <v>-0.2641</v>
       </c>
       <c r="V4" t="n">
         <v>1.788</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3955</v>
+        <v>1.0314</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2588</v>
+        <v>3.0837</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1367</v>
+        <v>-2.0523</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2528</v>
+        <v>-0.5544</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2084</v>
+        <v>-0.3164</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0444</v>
+        <v>-0.238</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2032</v>
+        <v>2.3511</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8249</v>
+        <v>1.0875</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6217</v>
+        <v>1.2635</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.456</v>
+        <v>-2.9054</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0333</v>
+        <v>-1.4039</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4227</v>
+        <v>-1.5015</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5576</v>
+        <v>0.9738</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5563</v>
+        <v>0.7326</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0013</v>
+        <v>0.2412</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4895</v>
+        <v>-1.9104</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1224</v>
+        <v>-1.9104</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3064</v>
+        <v>0.3337</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4269</v>
+        <v>0.4542</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3563</v>
@@ -922,13 +922,13 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.297</v>
+        <v>-0.2697</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.3776</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3252</v>
+        <v>-0.1979</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0136</v>
+        <v>0.1137</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3388</v>
+        <v>-0.3115</v>
       </c>
       <c r="G7" t="n">
         <v>0.3897</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.297</v>
+        <v>-0.1696</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0482</v>
+        <v>0.0519</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6119</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3266</v>
+        <v>-0.9351</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5705</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7561</v>
+        <v>-0.8651</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8877</v>
@@ -1078,13 +1078,13 @@
         <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3643</v>
+        <v>0.0272</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.387</v>
+        <v>0.1135</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0227</v>
+        <v>-0.0863</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0746</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4772</v>
+        <v>-1.441</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4408</v>
+        <v>-0.5409</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0364</v>
+        <v>-0.9001</v>
       </c>
       <c r="G9" t="n">
         <v>-0.656</v>
@@ -1156,13 +1156,13 @@
         <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6011</v>
+        <v>0.6373</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4508</v>
+        <v>0.3507</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1503</v>
+        <v>0.2866</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4522</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5589</v>
+        <v>-2.098</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2763</v>
+        <v>0.1847</v>
       </c>
       <c r="F10" t="n">
         <v>-2.2827</v>
@@ -1234,10 +1234,10 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4486</v>
+        <v>0.0123</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4116</v>
+        <v>0.0493</v>
       </c>
       <c r="U10" t="n">
         <v>-0.037</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3571</v>
+        <v>-2.6504</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9546</v>
+        <v>-0.1933</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4026</v>
+        <v>-2.4571</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6913</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4121</v>
+        <v>0.2947</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7145</v>
+        <v>0.0468</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3024</v>
+        <v>0.2479</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8358</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8923</v>
+        <v>-4.201</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9703</v>
+        <v>-4.4698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0779</v>
+        <v>0.2687</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7842</v>
@@ -1390,13 +1390,13 @@
         <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5514</v>
+        <v>0.1399</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.775</v>
+        <v>-0.2745</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2237</v>
+        <v>0.4144</v>
       </c>
       <c r="V12" t="n">
         <v>1.3836</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.129499999999998</v>
+        <v>-4.826699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7281</v>
+        <v>6.031099999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.8579</v>
+        <v>-10.8577</v>
       </c>
       <c r="G13" t="n">
         <v>-9.3407</v>
@@ -1468,19 +1468,19 @@
         <v>17.4628</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8542</v>
+        <v>3.1572</v>
       </c>
       <c r="T13" t="n">
-        <v>2.500799999999999</v>
+        <v>2.8036</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3535</v>
+        <v>0.3536000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.553700000000001</v>
+        <v>-1.5537</v>
       </c>
       <c r="W13" t="n">
-        <v>8.940100000000001</v>
+        <v>8.940099999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-10.4939</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3909</v>
+        <v>12.3948</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5811</v>
+        <v>11.1817</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8098</v>
+        <v>1.213</v>
       </c>
       <c r="G14" t="n">
         <v>4.9737</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4502</v>
+        <v>-0.4464</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9444</v>
+        <v>-0.3438</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5058</v>
+        <v>-0.1026</v>
       </c>
       <c r="V14" t="n">
         <v>5.7331</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8499</v>
+        <v>4.8354</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7363</v>
+        <v>3.8364</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1136</v>
+        <v>0.999</v>
       </c>
       <c r="G15" t="n">
         <v>3.2338</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3143</v>
+        <v>0.2997</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.581</v>
+        <v>-0.4809</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8953</v>
+        <v>0.7806</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0564</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>M. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3721</v>
+        <v>2.2482</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9457</v>
+        <v>2.1154</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5737</v>
+        <v>0.1329</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8938</v>
+        <v>0.3923</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7893</v>
+        <v>-1.7071</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1045</v>
+        <v>2.0994</v>
       </c>
       <c r="J16" t="n">
-        <v>1.424</v>
+        <v>1.9962</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4418</v>
+        <v>0.0247</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0178</v>
+        <v>1.9715</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5302</v>
+        <v>-1.6039</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6525</v>
+        <v>-1.7318</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1223</v>
+        <v>0.1279</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0305</v>
+        <v>-0.0665</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2382</v>
+        <v>-0.251</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2077</v>
+        <v>0.1845</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2239</v>
+        <v>0.5642</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4477</v>
+        <v>0.5642</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8357</v>
+        <v>1.6413</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6716</v>
+        <v>3.245</v>
       </c>
       <c r="F17" t="n">
-        <v>0.164</v>
+        <v>-1.6038</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7476</v>
+        <v>0.8938</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8628</v>
+        <v>0.7893</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1152</v>
+        <v>0.1045</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0519</v>
+        <v>1.424</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0113</v>
+        <v>1.4418</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0406</v>
+        <v>-0.0178</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3042</v>
+        <v>-0.5302</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1485</v>
+        <v>-0.6525</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1557</v>
+        <v>0.1223</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3284</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1146</v>
+        <v>0.2997</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9959</v>
+        <v>0.5375</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1187</v>
+        <v>-0.2378</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0564</v>
+        <v>1.2239</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0478</v>
+        <v>2.4477</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0086</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SANCHEZ SANCHEZ</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6904</v>
+        <v>1.2995</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0153</v>
+        <v>1.1711</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3248</v>
+        <v>0.1284</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3923</v>
+        <v>1.7476</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7071</v>
+        <v>1.8628</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0994</v>
+        <v>-0.1152</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9962</v>
+        <v>3.0519</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0247</v>
+        <v>3.0113</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9715</v>
+        <v>0.0406</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6039</v>
+        <v>-1.3042</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7318</v>
+        <v>-1.1485</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1279</v>
+        <v>-0.1557</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.3284</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.3582</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.194</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5523</v>
-      </c>
       <c r="S18" t="n">
-        <v>-0.6243</v>
+        <v>0.5785</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3511</v>
+        <v>0.4954</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2732</v>
+        <v>0.083</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5642</v>
+        <v>-0.0564</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5642</v>
+        <v>-0.0478</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.0086</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8773</v>
+        <v>-0.8228</v>
       </c>
       <c r="E19" t="n">
         <v>0.9671999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8445</v>
+        <v>-1.7899</v>
       </c>
       <c r="G19" t="n">
         <v>0.7565</v>
@@ -1936,13 +1936,13 @@
         <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1577</v>
+        <v>-0.1032</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V19" t="n">
         <v>-0.894</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9289</v>
+        <v>-1.1102</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5515</v>
+        <v>-2.3513</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6226</v>
+        <v>1.2411</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4334</v>
@@ -2014,13 +2014,13 @@
         <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8854</v>
+        <v>-0.0667</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3326</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3526</v>
+        <v>0.2658</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9982</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>R. LOPEZ RIVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9995</v>
+        <v>-1.9696</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2993</v>
+        <v>-1.7856</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7002</v>
+        <v>-0.184</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.301</v>
+        <v>-0.3417</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1485</v>
+        <v>-0.5157</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8475</v>
+        <v>0.1741</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2694</v>
+        <v>0.0818</v>
       </c>
       <c r="K21" t="n">
-        <v>0.206</v>
+        <v>0.0412</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0634</v>
+        <v>0.0406</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5704</v>
+        <v>-0.4235</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3545</v>
+        <v>-0.5569</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7841</v>
+        <v>0.1335</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.7463</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="V21" t="n">
         <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-0.5821</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.5821</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.5224</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.5358000000000001</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-1.1761</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. LOPEZ RIVERA</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2638</v>
+        <v>-2.0752</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7856</v>
+        <v>-0.3994</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4782</v>
+        <v>-1.6758</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3417</v>
+        <v>-0.301</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5157</v>
+        <v>-1.1485</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1741</v>
+        <v>0.8475</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0818</v>
+        <v>0.2694</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0412</v>
+        <v>0.206</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0406</v>
+        <v>0.0634</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4235</v>
+        <v>-0.5704</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5569</v>
+        <v>-1.3545</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1335</v>
+        <v>0.7841</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9403</v>
+        <v>-0.5821</v>
       </c>
       <c r="R22" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1759</v>
+        <v>-0.5981</v>
       </c>
       <c r="T22" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.0867</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2488</v>
+        <v>-0.5114</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7396</v>
+        <v>-3.2941</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.59</v>
+        <v>-3.7902</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1496</v>
+        <v>0.4961</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1857</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1393</v>
+        <v>0.3062</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1951</v>
+        <v>-0.0051</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3344</v>
+        <v>0.3113</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2803</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2003</v>
+        <v>-5.3483</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.163</v>
+        <v>-3.6625</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0374</v>
+        <v>-1.6858</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3954</v>
@@ -2326,13 +2326,13 @@
         <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3587</v>
+        <v>-0.5067</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3993</v>
+        <v>0.1012</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9594</v>
+        <v>-0.6079</v>
       </c>
       <c r="V24" t="n">
         <v>-1.506</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.129599999999998</v>
+        <v>7.799000000000001</v>
       </c>
       <c r="E25" t="n">
         <v>10.5278</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.398400000000001</v>
+        <v>-2.7288</v>
       </c>
       <c r="G25" t="n">
-        <v>9.3405</v>
+        <v>9.340499999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.276999999999999</v>
+        <v>1.277</v>
       </c>
       <c r="I25" t="n">
-        <v>8.063699999999999</v>
+        <v>8.063700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>18.1802</v>
@@ -2383,7 +2383,7 @@
         <v>13.3138</v>
       </c>
       <c r="L25" t="n">
-        <v>4.866300000000001</v>
+        <v>4.8663</v>
       </c>
       <c r="M25" t="n">
         <v>-8.839399999999999</v>
@@ -2404,13 +2404,13 @@
         <v>14.5524</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.8545</v>
+        <v>-0.1851999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3537000000000001</v>
+        <v>-0.3537</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.5008</v>
+        <v>0.1683</v>
       </c>
       <c r="V25" t="n">
         <v>1.553800000000001</v>
@@ -2419,7 +2419,7 @@
         <v>10.1641</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.610300000000001</v>
+        <v>-8.610299999999999</v>
       </c>
     </row>
   </sheetData>
